--- a/data/raw/raw summary cost data.xlsx
+++ b/data/raw/raw summary cost data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF701A85-208D-2144-8288-043606ED8B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DA06D1-6527-C441-8E30-B0ED37A11119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3660" yWindow="760" windowWidth="26580" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,9 +331,6 @@
     <t>IHR Coordination and National IHR Focal Point Functions</t>
   </si>
   <si>
-    <t>Zoonotic events and the human–animal interface</t>
-  </si>
-  <si>
     <t>Surveillance</t>
   </si>
   <si>
@@ -521,6 +518,9 @@
   </si>
   <si>
     <t>Radiation Events</t>
+  </si>
+  <si>
+    <t>Zoonotic events and the human-animal interface</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E4" s="2">
         <v>1547566</v>
@@ -995,7 +995,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2">
         <v>2165756</v>
@@ -1018,7 +1018,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6" s="1">
         <v>415719</v>
@@ -1041,7 +1041,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="1">
         <v>1059019</v>
@@ -1156,7 +1156,7 @@
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" s="1">
         <v>29984</v>
@@ -1202,7 +1202,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E14" s="1">
         <v>99881</v>
@@ -1271,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1">
         <v>898716</v>
@@ -1294,7 +1294,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E18" s="1">
         <v>181294</v>
@@ -1340,7 +1340,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E20" s="1">
         <v>169744</v>
@@ -1708,7 +1708,7 @@
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E36" s="1">
         <v>500000000</v>
@@ -1800,7 +1800,7 @@
         <v>14</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="1">
         <v>14283000</v>
@@ -2162,7 +2162,7 @@
         <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E56" s="1">
         <v>12025872</v>
@@ -2245,7 +2245,7 @@
         <v>14</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E60" s="1">
         <v>5492547</v>
@@ -2659,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2">
         <v>704080</v>
@@ -2751,7 +2751,7 @@
         <v>14</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E82" s="2">
         <v>2394825</v>
@@ -3119,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E98" s="3">
         <v>475046.67</v>
@@ -3211,7 +3211,7 @@
         <v>14</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E102" s="3">
         <v>2238841.7799999998</v>
@@ -3303,7 +3303,7 @@
         <v>14</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E106" s="2">
         <v>3965056</v>
@@ -3326,7 +3326,7 @@
         <v>14</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="E107" s="2">
         <v>2184075</v>
@@ -3349,7 +3349,7 @@
         <v>14</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E108" s="2">
         <v>2622819</v>
@@ -3372,7 +3372,7 @@
         <v>14</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E109" s="2">
         <v>6507557</v>
@@ -3441,7 +3441,7 @@
         <v>14</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E112" s="2">
         <v>21871396</v>
@@ -3487,7 +3487,7 @@
         <v>14</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E114" s="2">
         <v>37262878</v>
@@ -3533,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E116" s="2">
         <v>571606</v>
@@ -3556,7 +3556,7 @@
         <v>14</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E117" s="2">
         <v>6900995</v>
@@ -3579,7 +3579,7 @@
         <v>14</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E118" s="2">
         <v>606221</v>
@@ -3602,7 +3602,7 @@
         <v>14</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E119" s="2">
         <v>1711218</v>
@@ -3671,7 +3671,7 @@
         <v>14</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E122" s="2">
         <v>662055</v>
@@ -3688,7 +3688,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>35</v>
@@ -3703,7 +3703,7 @@
         <v>78</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -3711,7 +3711,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>14</v>
@@ -3726,7 +3726,7 @@
         <v>78</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -3734,7 +3734,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>14</v>
@@ -3749,7 +3749,7 @@
         <v>78</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -3757,7 +3757,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>14</v>
@@ -3772,7 +3772,7 @@
         <v>78</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -3780,7 +3780,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>14</v>
@@ -3795,7 +3795,7 @@
         <v>78</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -3803,7 +3803,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>14</v>
@@ -3818,7 +3818,7 @@
         <v>78</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -3826,7 +3826,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>14</v>
@@ -3841,7 +3841,7 @@
         <v>78</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -3849,7 +3849,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>14</v>
@@ -3864,7 +3864,7 @@
         <v>78</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -3872,7 +3872,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>14</v>
@@ -3887,7 +3887,7 @@
         <v>78</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -3895,7 +3895,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>14</v>
@@ -3910,7 +3910,7 @@
         <v>78</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -3918,7 +3918,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>14</v>
@@ -3933,7 +3933,7 @@
         <v>78</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -3941,7 +3941,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>14</v>
@@ -3956,7 +3956,7 @@
         <v>78</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -3964,7 +3964,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>14</v>
@@ -3979,7 +3979,7 @@
         <v>78</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -3987,7 +3987,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>14</v>
@@ -4002,7 +4002,7 @@
         <v>78</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -4010,7 +4010,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>14</v>
@@ -4025,7 +4025,7 @@
         <v>78</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -4033,13 +4033,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="E138" s="2">
         <v>174708</v>
@@ -4048,7 +4048,7 @@
         <v>78</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
@@ -4056,7 +4056,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>14</v>
@@ -4071,7 +4071,7 @@
         <v>78</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -4079,7 +4079,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>14</v>
@@ -4094,7 +4094,7 @@
         <v>78</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -4102,7 +4102,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>14</v>
@@ -4117,7 +4117,7 @@
         <v>78</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -4125,13 +4125,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E142" s="2">
         <v>5421278</v>
@@ -4140,7 +4140,7 @@
         <v>78</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -4148,7 +4148,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>35</v>
@@ -4163,7 +4163,7 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -4171,7 +4171,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>14</v>
@@ -4186,7 +4186,7 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -4194,7 +4194,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>14</v>
@@ -4209,7 +4209,7 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -4217,13 +4217,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E146" s="2">
         <v>1922152</v>
@@ -4232,7 +4232,7 @@
         <v>4</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -4240,13 +4240,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="E147" s="2">
         <v>1468086</v>
@@ -4255,7 +4255,7 @@
         <v>4</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -4263,13 +4263,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E148" s="2">
         <v>613709</v>
@@ -4278,7 +4278,7 @@
         <v>4</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -4286,13 +4286,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E149" s="2">
         <v>1518082</v>
@@ -4301,7 +4301,7 @@
         <v>4</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -4309,7 +4309,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>14</v>
@@ -4324,7 +4324,7 @@
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -4332,7 +4332,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>14</v>
@@ -4347,7 +4347,7 @@
         <v>4</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -4355,7 +4355,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>14</v>
@@ -4370,7 +4370,7 @@
         <v>4</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
@@ -4378,7 +4378,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>14</v>
@@ -4393,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
@@ -4401,13 +4401,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E154" s="2">
         <v>118398</v>
@@ -4416,7 +4416,7 @@
         <v>4</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
@@ -4424,7 +4424,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>14</v>
@@ -4439,7 +4439,7 @@
         <v>4</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
@@ -4447,13 +4447,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E156" s="2">
         <v>5908071</v>
@@ -4462,7 +4462,7 @@
         <v>4</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
@@ -4470,13 +4470,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E157" s="2">
         <v>179101</v>
@@ -4485,7 +4485,7 @@
         <v>4</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
@@ -4493,13 +4493,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E158" s="2">
         <v>257494</v>
@@ -4508,7 +4508,7 @@
         <v>4</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -4516,13 +4516,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E159" s="2">
         <v>3078049</v>
@@ -4531,7 +4531,7 @@
         <v>4</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -4539,7 +4539,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>14</v>
@@ -4554,7 +4554,7 @@
         <v>4</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
@@ -4562,7 +4562,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>14</v>
@@ -4577,7 +4577,7 @@
         <v>4</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
@@ -4585,13 +4585,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E162" s="2">
         <v>54520</v>
@@ -4600,7 +4600,7 @@
         <v>4</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
@@ -4608,7 +4608,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>35</v>
@@ -4620,10 +4620,10 @@
         <v>3807115500</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
@@ -4631,22 +4631,22 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E164" s="2">
         <v>1950000</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -4654,22 +4654,22 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E165" s="2">
         <v>1600000</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
@@ -4677,22 +4677,22 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E166" s="2">
         <v>90000000</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
@@ -4700,22 +4700,22 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E167" s="2">
         <v>637700000</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
@@ -4723,22 +4723,22 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E168" s="2">
         <v>1273100000</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
@@ -4746,22 +4746,22 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E169" s="2">
         <v>174420000</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
@@ -4769,22 +4769,22 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E170" s="2">
         <v>1000000</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
@@ -4792,7 +4792,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>14</v>
@@ -4804,10 +4804,10 @@
         <v>147000000</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
@@ -4815,7 +4815,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>14</v>
@@ -4827,10 +4827,10 @@
         <v>40000000</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
@@ -4838,7 +4838,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>14</v>
@@ -4850,10 +4850,10 @@
         <v>1000000</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
@@ -4861,22 +4861,22 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E174" s="2">
         <v>21220000</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
@@ -4884,7 +4884,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>14</v>
@@ -4896,10 +4896,10 @@
         <v>28300000</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
@@ -4907,22 +4907,22 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E176" s="2">
         <v>15700500</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
@@ -4930,22 +4930,22 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E177" s="2">
         <v>6000000</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
@@ -4953,22 +4953,22 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E178" s="2">
         <v>125100000</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
@@ -4976,22 +4976,22 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E179" s="2">
         <v>6825000</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -4999,7 +4999,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>14</v>
@@ -5011,10 +5011,10 @@
         <v>179400000</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -5022,7 +5022,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>14</v>
@@ -5034,10 +5034,10 @@
         <v>1045500000</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5045,22 +5045,22 @@
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E182" s="2">
         <v>11300000</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
@@ -5068,7 +5068,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>35</v>
@@ -5083,7 +5083,7 @@
         <v>58</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
@@ -5091,13 +5091,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E184" s="2">
         <v>164318</v>
@@ -5106,7 +5106,7 @@
         <v>58</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -5114,13 +5114,13 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E185" s="2">
         <v>788805</v>
@@ -5129,7 +5129,7 @@
         <v>58</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
@@ -5137,13 +5137,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E186" s="2">
         <v>3403830</v>
@@ -5152,7 +5152,7 @@
         <v>58</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
@@ -5160,13 +5160,13 @@
         <v>190</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E187" s="2">
         <v>4779094</v>
@@ -5175,7 +5175,7 @@
         <v>58</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
@@ -5183,13 +5183,13 @@
         <v>191</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E188" s="2">
         <v>1999377</v>
@@ -5198,7 +5198,7 @@
         <v>58</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
@@ -5206,13 +5206,13 @@
         <v>192</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E189" s="2">
         <v>4218107</v>
@@ -5221,7 +5221,7 @@
         <v>58</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
@@ -5229,7 +5229,7 @@
         <v>193</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>14</v>
@@ -5244,7 +5244,7 @@
         <v>58</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
@@ -5252,7 +5252,7 @@
         <v>197</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>14</v>
@@ -5267,7 +5267,7 @@
         <v>58</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
@@ -5275,7 +5275,7 @@
         <v>198</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>14</v>
@@ -5290,7 +5290,7 @@
         <v>58</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
@@ -5298,7 +5298,7 @@
         <v>199</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>14</v>
@@ -5313,7 +5313,7 @@
         <v>58</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
@@ -5321,13 +5321,13 @@
         <v>200</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E194" s="2">
         <v>11959114</v>
@@ -5336,7 +5336,7 @@
         <v>58</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
@@ -5344,7 +5344,7 @@
         <v>204</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>14</v>
@@ -5359,7 +5359,7 @@
         <v>58</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
@@ -5367,13 +5367,13 @@
         <v>205</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E196" s="2">
         <v>2767341</v>
@@ -5382,7 +5382,7 @@
         <v>58</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
@@ -5390,13 +5390,13 @@
         <v>206</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E197" s="2">
         <v>297864</v>
@@ -5405,7 +5405,7 @@
         <v>58</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
@@ -5413,13 +5413,13 @@
         <v>207</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E198" s="2">
         <v>373282</v>
@@ -5428,7 +5428,7 @@
         <v>58</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
@@ -5436,13 +5436,13 @@
         <v>208</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E199" s="2">
         <v>979534</v>
@@ -5451,7 +5451,7 @@
         <v>58</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -5459,7 +5459,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>14</v>
@@ -5474,7 +5474,7 @@
         <v>58</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
@@ -5482,7 +5482,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>14</v>
@@ -5497,7 +5497,7 @@
         <v>58</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
@@ -5505,13 +5505,13 @@
         <v>214</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E202" s="2">
         <v>1916809</v>
@@ -5520,7 +5520,7 @@
         <v>58</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
@@ -5528,13 +5528,13 @@
         <v>222</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E203" s="2">
         <v>247300</v>
@@ -5543,7 +5543,7 @@
         <v>74</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
@@ -5551,13 +5551,13 @@
         <v>223</v>
       </c>
       <c r="B204" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="E204" s="2">
         <v>415110</v>
@@ -5566,7 +5566,7 @@
         <v>74</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -5574,13 +5574,13 @@
         <v>224</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E205" s="2">
         <v>1054400</v>
@@ -5589,7 +5589,7 @@
         <v>74</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
@@ -5597,13 +5597,13 @@
         <v>225</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E206" s="2">
         <v>535275</v>
@@ -5612,7 +5612,7 @@
         <v>74</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -5620,13 +5620,13 @@
         <v>226</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E207" s="2">
         <v>4917340</v>
@@ -5635,7 +5635,7 @@
         <v>74</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
@@ -5643,13 +5643,13 @@
         <v>227</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E208" s="2">
         <v>322930</v>
@@ -5658,7 +5658,7 @@
         <v>74</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -5666,7 +5666,7 @@
         <v>228</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>14</v>
@@ -5681,7 +5681,7 @@
         <v>74</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -5689,7 +5689,7 @@
         <v>229</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>14</v>
@@ -5704,7 +5704,7 @@
         <v>74</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
@@ -5712,13 +5712,13 @@
         <v>230</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E211" s="2">
         <v>1930412</v>
@@ -5735,7 +5735,7 @@
         <v>231</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>14</v>
@@ -5750,7 +5750,7 @@
         <v>74</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -5758,13 +5758,13 @@
         <v>232</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E213" s="2">
         <v>520360</v>
@@ -5773,7 +5773,7 @@
         <v>74</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
@@ -5781,13 +5781,13 @@
         <v>233</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E214" s="2">
         <v>436420</v>
@@ -5796,7 +5796,7 @@
         <v>74</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
@@ -5804,13 +5804,13 @@
         <v>234</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E215" s="2">
         <v>255950</v>
@@ -5819,7 +5819,7 @@
         <v>74</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -5827,13 +5827,13 @@
         <v>235</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E216" s="2">
         <v>36440</v>
@@ -5850,13 +5850,13 @@
         <v>236</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E217" s="2">
         <v>673560</v>
@@ -5873,13 +5873,13 @@
         <v>237</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E218" s="2">
         <v>462055</v>
@@ -5888,7 +5888,7 @@
         <v>74</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
@@ -5896,7 +5896,7 @@
         <v>238</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>14</v>
@@ -5911,7 +5911,7 @@
         <v>74</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
@@ -5919,7 +5919,7 @@
         <v>239</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>14</v>
@@ -5934,7 +5934,7 @@
         <v>74</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
@@ -5942,13 +5942,13 @@
         <v>240</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E221" s="2">
         <v>177310</v>
@@ -5957,7 +5957,7 @@
         <v>74</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -5965,7 +5965,7 @@
         <v>241</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>35</v>
@@ -5980,7 +5980,7 @@
         <v>74</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -5988,22 +5988,22 @@
         <v>242</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E223" s="2">
         <v>2346091355</v>
       </c>
       <c r="F223" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
@@ -6011,22 +6011,22 @@
         <v>243</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E224" s="2">
         <v>2053518805</v>
       </c>
       <c r="F224" t="s">
+        <v>153</v>
+      </c>
+      <c r="G224" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
@@ -6034,22 +6034,22 @@
         <v>244</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E225" s="2">
         <v>27255662244</v>
       </c>
       <c r="F225" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
@@ -6057,22 +6057,22 @@
         <v>245</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E226" s="2">
         <v>5195094477</v>
       </c>
       <c r="F226" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
@@ -6080,22 +6080,22 @@
         <v>246</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E227" s="2">
         <v>10244621028</v>
       </c>
       <c r="F227" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -6103,22 +6103,22 @@
         <v>247</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E228" s="2">
         <v>2225685962</v>
       </c>
       <c r="F228" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -6126,7 +6126,7 @@
         <v>248</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>14</v>
@@ -6138,7 +6138,7 @@
         <v>8887960226</v>
       </c>
       <c r="F229" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>75</v>
@@ -6149,7 +6149,7 @@
         <v>249</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>14</v>
@@ -6161,10 +6161,10 @@
         <v>13484064490</v>
       </c>
       <c r="F230" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -6172,7 +6172,7 @@
         <v>250</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>14</v>
@@ -6184,7 +6184,7 @@
         <v>28723043437</v>
       </c>
       <c r="F231" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>59</v>
@@ -6195,7 +6195,7 @@
         <v>251</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>14</v>
@@ -6207,7 +6207,7 @@
         <v>7281805328</v>
       </c>
       <c r="F232" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>63</v>
@@ -6218,19 +6218,19 @@
         <v>252</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E233" s="2">
         <v>1464725845</v>
       </c>
       <c r="F233" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>66</v>
@@ -6241,7 +6241,7 @@
         <v>253</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>14</v>
@@ -6253,10 +6253,10 @@
         <v>1950922906</v>
       </c>
       <c r="F234" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
@@ -6264,19 +6264,19 @@
         <v>254</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E235" s="2">
         <v>885932730</v>
       </c>
       <c r="F235" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>70</v>
@@ -6287,22 +6287,22 @@
         <v>255</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E236" s="2">
         <v>11068089527</v>
       </c>
       <c r="F236" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -6310,22 +6310,22 @@
         <v>256</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E237" s="2">
         <v>14671014464</v>
       </c>
       <c r="F237" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -6333,22 +6333,22 @@
         <v>257</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E238" s="2">
         <v>10589643004</v>
       </c>
       <c r="F238" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -6356,7 +6356,7 @@
         <v>258</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>14</v>
@@ -6368,10 +6368,10 @@
         <v>3252244500</v>
       </c>
       <c r="F239" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -6379,7 +6379,7 @@
         <v>259</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>14</v>
@@ -6391,10 +6391,10 @@
         <v>4191108684</v>
       </c>
       <c r="F240" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
@@ -6402,19 +6402,19 @@
         <v>260</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E241" s="2">
         <v>4937711997</v>
       </c>
       <c r="F241" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>86</v>
@@ -6425,7 +6425,7 @@
         <v>261</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>35</v>
@@ -6437,10 +6437,10 @@
         <v>160708941019</v>
       </c>
       <c r="F242" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/raw summary cost data.xlsx
+++ b/data/raw/raw summary cost data.xlsx
@@ -8,19 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DA06D1-6527-C441-8E30-B0ED37A11119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0BD89F-6F21-0E4E-AC02-AE7B4525E19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3660" yWindow="760" windowWidth="26580" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="186">
   <si>
     <t>country</t>
   </si>
@@ -521,13 +533,70 @@
   </si>
   <si>
     <t>Zoonotic events and the human-animal interface</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>Legislation and Financing</t>
+  </si>
+  <si>
+    <t>USD (2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoonotic Disease </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food Safety </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biosafety and Biosecurity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunization </t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Laboratory System </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-Time Surveillance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reporting </t>
+  </si>
+  <si>
+    <t>Human Resoures (Animal and human health sector)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparedness </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency Response Operations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linking Public Health and Security Authorities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Countermeasures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk Communication </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Events Points of Entry (PoEs) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemical Events </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiation Emergencies </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,6 +609,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -562,20 +644,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -880,11 +965,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G242"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="16.83203125" style="1" customWidth="1"/>
@@ -5157,7 +5242,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>127</v>
@@ -5180,7 +5265,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>127</v>
@@ -5203,7 +5288,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>127</v>
@@ -5226,7 +5311,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>127</v>
@@ -5249,7 +5334,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>127</v>
@@ -5272,7 +5357,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>127</v>
@@ -5295,7 +5380,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>127</v>
@@ -5318,7 +5403,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>127</v>
@@ -5341,7 +5426,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>127</v>
@@ -5364,7 +5449,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>127</v>
@@ -5387,7 +5472,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>127</v>
@@ -5410,7 +5495,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>127</v>
@@ -5433,7 +5518,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>127</v>
@@ -5456,7 +5541,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>127</v>
@@ -5479,7 +5564,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>127</v>
@@ -5502,7 +5587,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>127</v>
@@ -5525,7 +5610,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>129</v>
@@ -5548,7 +5633,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>129</v>
@@ -5571,7 +5656,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>129</v>
@@ -5594,7 +5679,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>129</v>
@@ -5617,7 +5702,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>129</v>
@@ -5640,7 +5725,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>129</v>
@@ -5663,7 +5748,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>129</v>
@@ -5686,7 +5771,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>129</v>
@@ -5709,7 +5794,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>129</v>
@@ -5732,7 +5817,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>129</v>
@@ -5755,7 +5840,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>129</v>
@@ -5778,7 +5863,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>129</v>
@@ -5801,7 +5886,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>129</v>
@@ -5824,7 +5909,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>129</v>
@@ -5847,7 +5932,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>129</v>
@@ -5870,7 +5955,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>129</v>
@@ -5893,7 +5978,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>129</v>
@@ -5916,7 +6001,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>129</v>
@@ -5939,7 +6024,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>129</v>
@@ -5962,7 +6047,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>129</v>
@@ -5985,7 +6070,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>150</v>
@@ -5999,7 +6084,7 @@
       <c r="E223" s="2">
         <v>2346091355</v>
       </c>
-      <c r="F223" t="s">
+      <c r="F223" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G223" s="1" t="s">
@@ -6008,7 +6093,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>150</v>
@@ -6022,7 +6107,7 @@
       <c r="E224" s="2">
         <v>2053518805</v>
       </c>
-      <c r="F224" t="s">
+      <c r="F224" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G224" s="1" t="s">
@@ -6031,7 +6116,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>150</v>
@@ -6045,7 +6130,7 @@
       <c r="E225" s="2">
         <v>27255662244</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F225" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G225" s="1" t="s">
@@ -6054,7 +6139,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>150</v>
@@ -6068,7 +6153,7 @@
       <c r="E226" s="2">
         <v>5195094477</v>
       </c>
-      <c r="F226" t="s">
+      <c r="F226" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G226" s="1" t="s">
@@ -6077,7 +6162,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>150</v>
@@ -6091,7 +6176,7 @@
       <c r="E227" s="2">
         <v>10244621028</v>
       </c>
-      <c r="F227" t="s">
+      <c r="F227" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G227" s="1" t="s">
@@ -6100,7 +6185,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>150</v>
@@ -6114,7 +6199,7 @@
       <c r="E228" s="2">
         <v>2225685962</v>
       </c>
-      <c r="F228" t="s">
+      <c r="F228" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G228" s="1" t="s">
@@ -6123,7 +6208,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>150</v>
@@ -6137,7 +6222,7 @@
       <c r="E229" s="2">
         <v>8887960226</v>
       </c>
-      <c r="F229" t="s">
+      <c r="F229" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G229" s="1" t="s">
@@ -6146,7 +6231,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>150</v>
@@ -6160,7 +6245,7 @@
       <c r="E230" s="2">
         <v>13484064490</v>
       </c>
-      <c r="F230" t="s">
+      <c r="F230" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G230" s="1" t="s">
@@ -6169,7 +6254,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>150</v>
@@ -6183,7 +6268,7 @@
       <c r="E231" s="2">
         <v>28723043437</v>
       </c>
-      <c r="F231" t="s">
+      <c r="F231" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G231" s="1" t="s">
@@ -6192,7 +6277,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>150</v>
@@ -6206,7 +6291,7 @@
       <c r="E232" s="2">
         <v>7281805328</v>
       </c>
-      <c r="F232" t="s">
+      <c r="F232" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G232" s="1" t="s">
@@ -6215,7 +6300,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>150</v>
@@ -6229,7 +6314,7 @@
       <c r="E233" s="2">
         <v>1464725845</v>
       </c>
-      <c r="F233" t="s">
+      <c r="F233" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G233" s="1" t="s">
@@ -6238,7 +6323,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>150</v>
@@ -6252,7 +6337,7 @@
       <c r="E234" s="2">
         <v>1950922906</v>
       </c>
-      <c r="F234" t="s">
+      <c r="F234" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G234" s="1" t="s">
@@ -6261,7 +6346,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>150</v>
@@ -6275,7 +6360,7 @@
       <c r="E235" s="2">
         <v>885932730</v>
       </c>
-      <c r="F235" t="s">
+      <c r="F235" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G235" s="1" t="s">
@@ -6284,7 +6369,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>150</v>
@@ -6298,7 +6383,7 @@
       <c r="E236" s="2">
         <v>11068089527</v>
       </c>
-      <c r="F236" t="s">
+      <c r="F236" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G236" s="1" t="s">
@@ -6307,7 +6392,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>150</v>
@@ -6321,7 +6406,7 @@
       <c r="E237" s="2">
         <v>14671014464</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F237" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G237" s="1" t="s">
@@ -6330,7 +6415,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>150</v>
@@ -6344,7 +6429,7 @@
       <c r="E238" s="2">
         <v>10589643004</v>
       </c>
-      <c r="F238" t="s">
+      <c r="F238" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G238" s="1" t="s">
@@ -6353,7 +6438,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>150</v>
@@ -6367,7 +6452,7 @@
       <c r="E239" s="2">
         <v>3252244500</v>
       </c>
-      <c r="F239" t="s">
+      <c r="F239" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G239" s="1" t="s">
@@ -6376,7 +6461,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>150</v>
@@ -6390,7 +6475,7 @@
       <c r="E240" s="2">
         <v>4191108684</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F240" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G240" s="1" t="s">
@@ -6399,7 +6484,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>150</v>
@@ -6413,7 +6498,7 @@
       <c r="E241" s="2">
         <v>4937711997</v>
       </c>
-      <c r="F241" t="s">
+      <c r="F241" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G241" s="1" t="s">
@@ -6422,7 +6507,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>150</v>
@@ -6436,11 +6521,471 @@
       <c r="E242" s="2">
         <v>160708941019</v>
       </c>
-      <c r="F242" t="s">
+      <c r="F242" s="5" t="s">
         <v>153</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E243" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E244" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E245" s="6">
+        <v>44500</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E246" s="6">
+        <v>73000</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E247" s="6">
+        <v>71000</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E248" s="6">
+        <v>1164000</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E249" s="6">
+        <v>84500</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E250" s="6">
+        <v>691000</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E251" s="6">
+        <v>92500</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E252" s="6">
+        <v>22500</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E253" s="6">
+        <v>16000</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E254" s="6">
+        <v>37000</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E255" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E256" s="6">
+        <v>30000</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E257" s="6">
+        <v>70000</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D258" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E258" s="6">
+        <v>39000</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E259" s="6">
+        <v>22500</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E260" s="6">
+        <v>220000</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E261" s="6">
+        <v>710000</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D262" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E262" s="7">
+        <v>3408000</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/raw summary cost data.xlsx
+++ b/data/raw/raw summary cost data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0BD89F-6F21-0E4E-AC02-AE7B4525E19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DF0E84-7153-1F40-AA5B-996E9D1C08DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3660" yWindow="760" windowWidth="26580" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="203">
   <si>
     <t>country</t>
   </si>
@@ -253,9 +253,6 @@
     <t>page 10</t>
   </si>
   <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
     <t>USD (2020)</t>
   </si>
   <si>
@@ -541,9 +538,6 @@
     <t>Legislation and Financing</t>
   </si>
   <si>
-    <t>USD (2023)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zoonotic Disease </t>
   </si>
   <si>
@@ -590,6 +584,63 @@
   </si>
   <si>
     <t xml:space="preserve">Radiation Emergencies </t>
+  </si>
+  <si>
+    <t>USD (2024)</t>
+  </si>
+  <si>
+    <t>Cameroon</t>
+  </si>
+  <si>
+    <t>USD (2021)</t>
+  </si>
+  <si>
+    <t>National legislation, policy, and financing</t>
+  </si>
+  <si>
+    <t>IHR coordination, communication, and advocacy</t>
+  </si>
+  <si>
+    <t>Antimicrobial resistance</t>
+  </si>
+  <si>
+    <t>Zoonotic disease</t>
+  </si>
+  <si>
+    <t>Food safety</t>
+  </si>
+  <si>
+    <t>Biosafety and biosecurity</t>
+  </si>
+  <si>
+    <t>National laboratory system</t>
+  </si>
+  <si>
+    <t>Human resources</t>
+  </si>
+  <si>
+    <t>Emergency preparedness</t>
+  </si>
+  <si>
+    <t>Linking public health and security authorities</t>
+  </si>
+  <si>
+    <t>Emergency response operations</t>
+  </si>
+  <si>
+    <t>Medical countermeasures and personnel deployment</t>
+  </si>
+  <si>
+    <t>Risk communication</t>
+  </si>
+  <si>
+    <t>Points of entry</t>
+  </si>
+  <si>
+    <t>Chemical events</t>
+  </si>
+  <si>
+    <t>Radiation emergencies</t>
   </si>
 </sst>
 </file>
@@ -617,9 +668,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -644,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -660,7 +710,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -965,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G281"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
@@ -1057,7 +1116,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E4" s="2">
         <v>1547566</v>
@@ -1080,7 +1139,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E5" s="2">
         <v>2165756</v>
@@ -1103,7 +1162,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E6" s="1">
         <v>415719</v>
@@ -1126,7 +1185,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="1">
         <v>1059019</v>
@@ -1241,7 +1300,7 @@
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E12" s="1">
         <v>29984</v>
@@ -1287,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="1">
         <v>99881</v>
@@ -1356,7 +1415,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" s="1">
         <v>898716</v>
@@ -1379,7 +1438,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E18" s="1">
         <v>181294</v>
@@ -1425,7 +1484,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="1">
         <v>169744</v>
@@ -1793,7 +1852,7 @@
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="1">
         <v>500000000</v>
@@ -1885,7 +1944,7 @@
         <v>14</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E40" s="1">
         <v>14283000</v>
@@ -2247,7 +2306,7 @@
         <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E56" s="1">
         <v>12025872</v>
@@ -2330,7 +2389,7 @@
         <v>14</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E60" s="1">
         <v>5492547</v>
@@ -2370,7 +2429,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>35</v>
@@ -2379,13 +2438,13 @@
         <v>35</v>
       </c>
       <c r="E62" s="2">
-        <v>308462389</v>
+        <v>154392676</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
@@ -2393,22 +2452,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E63" s="2">
-        <v>154392676</v>
+        <v>142700</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -2416,22 +2475,22 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E64" s="2">
-        <v>142700</v>
+        <v>4510088</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
@@ -2439,22 +2498,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E65" s="2">
-        <v>4510088</v>
+        <v>2350245</v>
       </c>
       <c r="F65" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -2462,22 +2521,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E66" s="2">
-        <v>2350245</v>
+        <v>6532750</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -2485,22 +2544,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E67" s="2">
-        <v>6532750</v>
+        <v>6836485</v>
       </c>
       <c r="F67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -2508,22 +2567,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E68" s="2">
-        <v>6836485</v>
+        <v>363950</v>
       </c>
       <c r="F68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -2531,22 +2590,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E69" s="2">
-        <v>363950</v>
+        <v>4035625</v>
       </c>
       <c r="F69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -2554,22 +2613,22 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E70" s="2">
-        <v>4035625</v>
+        <v>25522515</v>
       </c>
       <c r="F70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -2577,22 +2636,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E71" s="2">
-        <v>25522515</v>
+        <v>34678870</v>
       </c>
       <c r="F71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -2600,22 +2659,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E72" s="2">
-        <v>34678870</v>
+        <v>958700</v>
       </c>
       <c r="F72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -2623,22 +2682,22 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E73" s="2">
-        <v>958700</v>
+        <v>39948620</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
@@ -2646,22 +2705,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E74" s="2">
-        <v>39948620</v>
+        <v>8848123</v>
       </c>
       <c r="F74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
@@ -2669,22 +2728,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E75" s="2">
-        <v>8848123</v>
+        <v>1328140</v>
       </c>
       <c r="F75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
@@ -2692,22 +2751,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E76" s="2">
-        <v>1328140</v>
+        <v>5751850</v>
       </c>
       <c r="F76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -2715,22 +2774,22 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="E77" s="2">
-        <v>5751850</v>
+        <v>704080</v>
       </c>
       <c r="F77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
@@ -2738,22 +2797,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E78" s="2">
-        <v>704080</v>
+        <v>4509051</v>
       </c>
       <c r="F78" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
@@ -2761,22 +2820,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E79" s="2">
-        <v>4509051</v>
+        <v>1517095</v>
       </c>
       <c r="F79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -2784,22 +2843,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E80" s="2">
-        <v>1517095</v>
+        <v>3458965</v>
       </c>
       <c r="F80" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
@@ -2807,22 +2866,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E81" s="2">
-        <v>3458965</v>
+        <v>2394825</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
@@ -2830,19 +2889,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E82" s="2">
-        <v>2394825</v>
+        <v>158524934</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>79</v>
@@ -2853,22 +2912,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="2">
-        <v>158524934</v>
+        <v>37</v>
+      </c>
+      <c r="E83" s="3">
+        <v>254347.31</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
@@ -2876,22 +2935,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E84" s="2">
+        <v>491528.85</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E84" s="3">
-        <v>254347.31</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
@@ -2899,22 +2958,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E85" s="2">
-        <v>491528.85</v>
+        <v>5399801.4699999997</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
@@ -2922,22 +2981,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E86" s="2">
-        <v>5399801.4699999997</v>
+        <v>20652080.449999999</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -2945,22 +3004,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E87" s="2">
-        <v>20652080.449999999</v>
+        <v>43</v>
+      </c>
+      <c r="E87" s="3">
+        <v>343208.4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -2968,19 +3027,19 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E88" s="3">
-        <v>343208.4</v>
+        <v>15011529.810000001</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>84</v>
@@ -2991,19 +3050,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E89" s="3">
-        <v>15011529.810000001</v>
+        <v>45</v>
+      </c>
+      <c r="E89" s="2">
+        <v>46746771.740000002</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>85</v>
@@ -3014,19 +3073,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E90" s="2">
-        <v>46746771.740000002</v>
+        <v>46</v>
+      </c>
+      <c r="E90" s="3">
+        <v>32333141.93</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>86</v>
@@ -3037,19 +3096,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E91" s="3">
-        <v>32333141.93</v>
+        <v>2575316.6</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>87</v>
@@ -3060,19 +3119,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E92" s="3">
-        <v>2575316.6</v>
+        <v>48</v>
+      </c>
+      <c r="E92" s="2">
+        <v>181497.88</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>88</v>
@@ -3083,19 +3142,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E93" s="2">
-        <v>181497.88</v>
+        <v>3505474.36</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>89</v>
@@ -3106,19 +3165,19 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E94" s="2">
-        <v>3505474.36</v>
+        <v>498907.05</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>90</v>
@@ -3129,19 +3188,19 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E95" s="2">
-        <v>498907.05</v>
+        <v>1121472.23</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>91</v>
@@ -3152,19 +3211,19 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E96" s="2">
-        <v>1121472.23</v>
+        <v>53</v>
+      </c>
+      <c r="E96" s="3">
+        <v>83019.23</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>92</v>
@@ -3175,19 +3234,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="E97" s="3">
-        <v>83019.23</v>
+        <v>475046.67</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>93</v>
@@ -3198,19 +3257,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E98" s="3">
-        <v>475046.67</v>
+        <v>242627.18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>94</v>
@@ -3221,19 +3280,19 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E99" s="3">
-        <v>242627.18</v>
+        <v>3692639.83</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>95</v>
@@ -3244,19 +3303,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E100" s="3">
-        <v>3692639.83</v>
+        <v>56</v>
+      </c>
+      <c r="E100" s="2">
+        <v>22585312.48</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>96</v>
@@ -3267,19 +3326,19 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E101" s="2">
-        <v>22585312.48</v>
+        <v>125</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2238841.7799999998</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>97</v>
@@ -3290,22 +3349,22 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E102" s="3">
-        <v>2238841.7799999998</v>
+        <v>35</v>
+      </c>
+      <c r="E102" s="2">
+        <v>439123340</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -3313,114 +3372,114 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E103" s="2">
+        <v>1332898</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G103" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="2">
-        <v>439123340</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E104" s="2">
+        <v>2374296</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G104" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E104" s="2">
-        <v>1332898</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E105" s="2">
+        <v>3965056</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E105" s="2">
-        <v>2374296</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2184075</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E106" s="2">
-        <v>3965056</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="2">
+        <v>2622819</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G107" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E107" s="2">
-        <v>2184075</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
@@ -3428,22 +3487,22 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E108" s="2">
+        <v>6507557</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E108" s="2">
-        <v>2622819</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
@@ -3451,22 +3510,22 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E109" s="2">
+        <v>264556777</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E109" s="2">
-        <v>6507557</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -3474,22 +3533,22 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="2">
+        <v>35310127</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E110" s="2">
-        <v>264556777</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
@@ -3497,22 +3556,22 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E111" s="2">
+        <v>21871396</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G111" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E111" s="2">
-        <v>35310127</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
@@ -3520,114 +3579,114 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="2">
+        <v>7384103</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E112" s="2">
-        <v>21871396</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E113" s="2">
+        <v>37262878</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E113" s="2">
-        <v>7384103</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="2">
+        <v>36972150</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E114" s="2">
-        <v>37262878</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E115" s="2">
+        <v>571606</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="2">
-        <v>36972150</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E116" s="2">
+        <v>6900995</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E116" s="2">
-        <v>571606</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -3635,7 +3694,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>14</v>
@@ -3644,13 +3703,13 @@
         <v>105</v>
       </c>
       <c r="E117" s="2">
-        <v>6900995</v>
+        <v>606221</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
@@ -3658,7 +3717,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>14</v>
@@ -3667,13 +3726,13 @@
         <v>106</v>
       </c>
       <c r="E118" s="2">
-        <v>606221</v>
+        <v>1711218</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
@@ -3681,22 +3740,22 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E119" s="2">
+        <v>4277156</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G119" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E119" s="2">
-        <v>1711218</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
@@ -3704,22 +3763,22 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E120" s="2">
+        <v>2049957</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G120" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E120" s="2">
-        <v>4277156</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -3727,22 +3786,22 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E121" s="2">
+        <v>662055</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E121" s="2">
-        <v>2049957</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
@@ -3750,22 +3809,22 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E122" s="2">
-        <v>662055</v>
+        <v>291130326</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -3773,22 +3832,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E123" s="2">
-        <v>291130326</v>
+        <v>210735</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -3796,22 +3855,22 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E124" s="2">
-        <v>210735</v>
+        <v>2074103</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -3819,22 +3878,22 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E125" s="2">
-        <v>2074103</v>
+        <v>13615857</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -3842,22 +3901,22 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E126" s="2">
-        <v>13615857</v>
+        <v>13674069</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -3865,22 +3924,22 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E127" s="2">
-        <v>13674069</v>
+        <v>2782264</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -3888,22 +3947,22 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E128" s="2">
-        <v>2782264</v>
+        <v>2909178</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -3911,22 +3970,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E129" s="2">
-        <v>2909178</v>
+        <v>54136709</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -3934,22 +3993,22 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E130" s="2">
-        <v>54136709</v>
+        <v>11824545</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -3957,22 +4016,22 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E131" s="2">
-        <v>11824545</v>
+        <v>141708348</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -3980,22 +4039,22 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E132" s="2">
-        <v>141708348</v>
+        <v>194308</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -4003,22 +4062,22 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E133" s="2">
-        <v>194308</v>
+        <v>1867037</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -4026,22 +4085,22 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E134" s="2">
-        <v>1867037</v>
+        <v>972981</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -4049,22 +4108,22 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E135" s="2">
-        <v>972981</v>
+        <v>6251366</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -4072,22 +4131,22 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E136" s="2">
-        <v>6251366</v>
+        <v>359687</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -4095,22 +4154,22 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E137" s="2">
-        <v>359687</v>
+        <v>174708</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -4118,22 +4177,22 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D138" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E138" s="2">
+        <v>2829652</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G138" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E138" s="2">
-        <v>174708</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
@@ -4141,22 +4200,22 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E139" s="2">
-        <v>2829652</v>
+        <v>6211824</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -4164,22 +4223,22 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E140" s="2">
-        <v>6211824</v>
+        <v>23911675</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -4187,22 +4246,22 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E141" s="2">
-        <v>23911675</v>
+        <v>5421278</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -4210,22 +4269,22 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E142" s="2">
-        <v>5421278</v>
+        <v>69067059</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -4233,22 +4292,22 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E143" s="2">
-        <v>69067059</v>
+        <v>1473169</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -4256,7 +4315,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>14</v>
@@ -4265,13 +4324,13 @@
         <v>101</v>
       </c>
       <c r="E144" s="2">
-        <v>1473169</v>
+        <v>625967</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -4279,22 +4338,22 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="E145" s="2">
-        <v>625967</v>
+        <v>1922152</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -4302,22 +4361,22 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E146" s="2">
-        <v>1922152</v>
+        <v>1468086</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -4325,22 +4384,22 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="E147" s="2">
-        <v>1468086</v>
+        <v>613709</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -4348,22 +4407,22 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E148" s="2">
-        <v>613709</v>
+        <v>1518082</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -4371,22 +4430,22 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="E149" s="2">
-        <v>1518082</v>
+        <v>36961929</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -4394,22 +4453,22 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E150" s="2">
-        <v>36961929</v>
+        <v>6327276</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -4417,22 +4476,22 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E151" s="2">
-        <v>6327276</v>
+        <v>3907102</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -4440,22 +4499,22 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E152" s="2">
-        <v>3907102</v>
+        <v>1116072</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
@@ -4463,22 +4522,22 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="E153" s="2">
-        <v>1116072</v>
+        <v>118398</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
@@ -4486,22 +4545,22 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="E154" s="2">
-        <v>118398</v>
+        <v>614431</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
@@ -4509,22 +4568,22 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="E155" s="2">
-        <v>614431</v>
+        <v>5908071</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
@@ -4532,22 +4591,22 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E156" s="2">
-        <v>5908071</v>
+        <v>179101</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
@@ -4555,22 +4614,22 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E157" s="2">
-        <v>179101</v>
+        <v>257494</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
@@ -4578,7 +4637,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>14</v>
@@ -4587,13 +4646,13 @@
         <v>106</v>
       </c>
       <c r="E158" s="2">
-        <v>257494</v>
+        <v>3078049</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -4601,22 +4660,22 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="E159" s="2">
-        <v>3078049</v>
+        <v>2544366</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -4624,22 +4683,22 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E160" s="2">
-        <v>2544366</v>
+        <v>379085</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
@@ -4647,22 +4706,22 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E161" s="2">
-        <v>379085</v>
+        <v>54520</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
@@ -4670,22 +4729,22 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E162" s="2">
-        <v>54520</v>
+        <v>3807115500</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
@@ -4693,22 +4752,22 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E163" s="2">
+        <v>1950000</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G163" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E163" s="2">
-        <v>3807115500</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
@@ -4716,7 +4775,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>14</v>
@@ -4725,13 +4784,13 @@
         <v>117</v>
       </c>
       <c r="E164" s="2">
-        <v>1950000</v>
+        <v>1600000</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -4739,22 +4798,22 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E165" s="2">
+        <v>90000000</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E165" s="2">
-        <v>1600000</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
@@ -4762,22 +4821,22 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E166" s="2">
+        <v>637700000</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G166" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E166" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
@@ -4785,22 +4844,22 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E167" s="2">
+        <v>1273100000</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G167" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E167" s="2">
-        <v>637700000</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
@@ -4808,22 +4867,22 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E168" s="2">
+        <v>174420000</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G168" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E168" s="2">
-        <v>1273100000</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
@@ -4831,22 +4890,22 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E169" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G169" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E169" s="2">
-        <v>174420000</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
@@ -4854,22 +4913,22 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E170" s="2">
+        <v>147000000</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G170" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E170" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
@@ -4877,22 +4936,22 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G171" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E171" s="2">
-        <v>147000000</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
@@ -4900,22 +4959,22 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G172" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E172" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
@@ -4923,22 +4982,22 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E173" s="2">
+        <v>21220000</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G173" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E173" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
@@ -4946,22 +5005,22 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="2">
+        <v>28300000</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G174" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E174" s="2">
-        <v>21220000</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
@@ -4969,22 +5028,22 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E175" s="2">
+        <v>15700500</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G175" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E175" s="2">
-        <v>28300000</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
@@ -4992,22 +5051,22 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E176" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G176" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E176" s="2">
-        <v>15700500</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
@@ -5015,22 +5074,22 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E177" s="2">
+        <v>125100000</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G177" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E177" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
@@ -5038,22 +5097,22 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E178" s="2">
+        <v>6825000</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G178" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E178" s="2">
-        <v>125100000</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
@@ -5061,22 +5120,22 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E179" s="2">
+        <v>179400000</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G179" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E179" s="2">
-        <v>6825000</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -5084,22 +5143,22 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E180" s="2">
+        <v>1045500000</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G180" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E180" s="2">
-        <v>179400000</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -5107,22 +5166,22 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E181" s="2">
+        <v>11300000</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G181" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E181" s="2">
-        <v>1045500000</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5130,22 +5189,22 @@
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E182" s="2">
-        <v>11300000</v>
+        <v>603158558</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
@@ -5153,22 +5212,22 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E183" s="2">
-        <v>603158558</v>
+        <v>164318</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
@@ -5176,7 +5235,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>14</v>
@@ -5185,13 +5244,13 @@
         <v>117</v>
       </c>
       <c r="E184" s="2">
-        <v>164318</v>
+        <v>788805</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -5199,22 +5258,22 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="E185" s="2">
-        <v>788805</v>
+        <v>3403830</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
@@ -5222,22 +5281,22 @@
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="E186" s="2">
-        <v>3403830</v>
+        <v>4779094</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
@@ -5245,22 +5304,22 @@
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E187" s="2">
-        <v>4779094</v>
+        <v>1999377</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
@@ -5268,22 +5327,22 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E188" s="2">
-        <v>1999377</v>
+        <v>4218107</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
@@ -5291,22 +5350,22 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="E189" s="2">
-        <v>4218107</v>
+        <v>523498273</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
@@ -5314,22 +5373,22 @@
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E190" s="2">
-        <v>523498273</v>
+        <v>31429402</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
@@ -5337,22 +5396,22 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E191" s="2">
-        <v>31429402</v>
+        <v>6899134</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
@@ -5360,22 +5419,22 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E192" s="2">
-        <v>6899134</v>
+        <v>41723</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
@@ -5383,22 +5442,22 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="E193" s="2">
-        <v>41723</v>
+        <v>11959114</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
@@ -5406,22 +5465,22 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="E194" s="2">
-        <v>11959114</v>
+        <v>432761</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
@@ -5429,22 +5488,22 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="E195" s="2">
-        <v>432761</v>
+        <v>2767341</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
@@ -5452,22 +5511,22 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E196" s="2">
-        <v>2767341</v>
+        <v>297864</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
@@ -5475,22 +5534,22 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E197" s="2">
-        <v>297864</v>
+        <v>373282</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
@@ -5498,7 +5557,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>14</v>
@@ -5507,13 +5566,13 @@
         <v>106</v>
       </c>
       <c r="E198" s="2">
-        <v>373282</v>
+        <v>979534</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
@@ -5521,22 +5580,22 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="E199" s="2">
-        <v>979534</v>
+        <v>6386634</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -5544,22 +5603,22 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E200" s="2">
-        <v>6386634</v>
+        <v>978057</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
@@ -5567,22 +5626,22 @@
         <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E201" s="2">
-        <v>978057</v>
+        <v>1916809</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
@@ -5590,22 +5649,22 @@
         <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E202" s="2">
-        <v>1916809</v>
+        <v>247300</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
@@ -5613,22 +5672,22 @@
         <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="E203" s="2">
-        <v>247300</v>
+        <v>415110</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
@@ -5636,19 +5695,19 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E204" s="2">
-        <v>415110</v>
+        <v>1054400</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>133</v>
@@ -5659,19 +5718,19 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E205" s="2">
-        <v>1054400</v>
+        <v>535275</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>134</v>
@@ -5682,19 +5741,19 @@
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E206" s="2">
-        <v>535275</v>
+        <v>4917340</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>135</v>
@@ -5705,19 +5764,19 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E207" s="2">
-        <v>4917340</v>
+        <v>322930</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>136</v>
@@ -5728,22 +5787,22 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="E208" s="2">
-        <v>322930</v>
+        <v>914716</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -5751,22 +5810,22 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E209" s="2">
-        <v>914716</v>
+        <v>3636990</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -5774,22 +5833,22 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="E210" s="2">
-        <v>3636990</v>
+        <v>1930412</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
@@ -5797,22 +5856,22 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E211" s="2">
-        <v>1930412</v>
+        <v>8</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
@@ -5820,22 +5879,22 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>67</v>
+        <v>140</v>
+      </c>
+      <c r="E212" s="2">
+        <v>520360</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -5843,19 +5902,19 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E213" s="2">
-        <v>520360</v>
+        <v>436420</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>142</v>
@@ -5866,22 +5925,22 @@
         <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D214" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E214" s="2">
+        <v>255950</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G214" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="E214" s="2">
-        <v>436420</v>
-      </c>
-      <c r="F214" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
@@ -5889,22 +5948,22 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E215" s="2">
-        <v>255950</v>
+        <v>36440</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -5912,22 +5971,22 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E216" s="2">
-        <v>36440</v>
+        <v>673560</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
@@ -5935,7 +5994,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>14</v>
@@ -5944,13 +6003,13 @@
         <v>106</v>
       </c>
       <c r="E217" s="2">
-        <v>673560</v>
+        <v>462055</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
@@ -5958,19 +6017,19 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="E218" s="2">
-        <v>462055</v>
+        <v>1271060</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>146</v>
@@ -5981,19 +6040,19 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E219" s="2">
-        <v>1271060</v>
+        <v>49840</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>147</v>
@@ -6004,19 +6063,19 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E220" s="2">
-        <v>49840</v>
+        <v>177310</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>148</v>
@@ -6027,22 +6086,22 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E221" s="2">
-        <v>177310</v>
+        <v>17857468</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -6050,22 +6109,22 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E222" s="2">
-        <v>17857468</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>74</v>
+        <v>2346091355</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -6073,7 +6132,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>14</v>
@@ -6082,13 +6141,13 @@
         <v>117</v>
       </c>
       <c r="E223" s="2">
-        <v>2346091355</v>
+        <v>2053518805</v>
       </c>
       <c r="F223" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G223" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
@@ -6096,19 +6155,19 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="E224" s="2">
-        <v>2053518805</v>
+        <v>27255662244</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>154</v>
@@ -6119,22 +6178,22 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="E225" s="2">
-        <v>27255662244</v>
+        <v>5195094477</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
@@ -6142,22 +6201,22 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E226" s="2">
-        <v>5195094477</v>
+        <v>10244621028</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
@@ -6165,22 +6224,22 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E227" s="2">
-        <v>10244621028</v>
+        <v>2225685962</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -6188,22 +6247,22 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="E228" s="2">
-        <v>2225685962</v>
+        <v>8887960226</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -6211,22 +6270,22 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E229" s="2">
-        <v>8887960226</v>
+        <v>13484064490</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -6234,22 +6293,22 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E230" s="2">
-        <v>13484064490</v>
+        <v>28723043437</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -6257,22 +6316,22 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E231" s="2">
-        <v>28723043437</v>
+        <v>7281805328</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -6280,22 +6339,22 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="E232" s="2">
-        <v>7281805328</v>
+        <v>1464725845</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
@@ -6303,22 +6362,22 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="E233" s="2">
-        <v>1464725845</v>
+        <v>1950922906</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -6326,22 +6385,22 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="E234" s="2">
-        <v>1950922906</v>
+        <v>885932730</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
@@ -6349,22 +6408,22 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E235" s="2">
-        <v>885932730</v>
+        <v>11068089527</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -6372,22 +6431,22 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E236" s="2">
-        <v>11068089527</v>
+        <v>14671014464</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -6395,7 +6454,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>14</v>
@@ -6404,10 +6463,10 @@
         <v>106</v>
       </c>
       <c r="E237" s="2">
-        <v>14671014464</v>
+        <v>10589643004</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>158</v>
@@ -6418,19 +6477,19 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="E238" s="2">
-        <v>10589643004</v>
+        <v>3252244500</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>159</v>
@@ -6441,19 +6500,19 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E239" s="2">
-        <v>3252244500</v>
+        <v>4191108684</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>160</v>
@@ -6464,22 +6523,22 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E240" s="2">
-        <v>4191108684</v>
+        <v>4937711997</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
@@ -6487,22 +6546,22 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E241" s="2">
-        <v>4937711997</v>
+        <v>160708941019</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -6510,22 +6569,22 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="E242" s="2">
-        <v>160708941019</v>
-      </c>
-      <c r="F242" s="5" t="s">
-        <v>153</v>
+        <v>6000</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -6533,22 +6592,22 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="E243" s="2">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
@@ -6556,22 +6615,22 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="E244" s="2">
-        <v>4500</v>
+        <v>44500</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
@@ -6579,22 +6638,22 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D245" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E245" s="6">
-        <v>44500</v>
+      <c r="D245" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E245" s="2">
+        <v>73000</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
@@ -6602,22 +6661,22 @@
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E246" s="6">
-        <v>73000</v>
+        <v>169</v>
+      </c>
+      <c r="E246" s="2">
+        <v>71000</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -6625,22 +6684,22 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E247" s="6">
-        <v>71000</v>
+        <v>170</v>
+      </c>
+      <c r="E247" s="2">
+        <v>1164000</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
@@ -6648,22 +6707,22 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E248" s="6">
-        <v>1164000</v>
+        <v>171</v>
+      </c>
+      <c r="E248" s="2">
+        <v>84500</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
@@ -6671,22 +6730,22 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E249" s="6">
-        <v>84500</v>
+        <v>172</v>
+      </c>
+      <c r="E249" s="2">
+        <v>691000</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
@@ -6694,22 +6753,22 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E250" s="6">
-        <v>691000</v>
+        <v>173</v>
+      </c>
+      <c r="E250" s="2">
+        <v>92500</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -6717,22 +6776,22 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E251" s="6">
-        <v>92500</v>
+        <v>174</v>
+      </c>
+      <c r="E251" s="2">
+        <v>22500</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
@@ -6740,22 +6799,22 @@
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E252" s="6">
-        <v>22500</v>
+        <v>175</v>
+      </c>
+      <c r="E252" s="2">
+        <v>16000</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -6763,22 +6822,22 @@
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E253" s="6">
-        <v>16000</v>
+        <v>176</v>
+      </c>
+      <c r="E253" s="2">
+        <v>37000</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -6786,22 +6845,22 @@
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E254" s="6">
-        <v>37000</v>
+        <v>177</v>
+      </c>
+      <c r="E254" s="2">
+        <v>10000</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
@@ -6809,22 +6868,22 @@
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E255" s="6">
-        <v>10000</v>
+        <v>178</v>
+      </c>
+      <c r="E255" s="2">
+        <v>30000</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
@@ -6832,22 +6891,22 @@
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E256" s="6">
-        <v>30000</v>
+        <v>179</v>
+      </c>
+      <c r="E256" s="2">
+        <v>70000</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
@@ -6855,22 +6914,22 @@
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E257" s="6">
-        <v>70000</v>
+        <v>180</v>
+      </c>
+      <c r="E257" s="2">
+        <v>39000</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -6878,22 +6937,22 @@
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E258" s="6">
-        <v>39000</v>
+        <v>181</v>
+      </c>
+      <c r="E258" s="2">
+        <v>22500</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
@@ -6901,22 +6960,22 @@
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E259" s="6">
-        <v>22500</v>
+        <v>182</v>
+      </c>
+      <c r="E259" s="2">
+        <v>220000</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
@@ -6924,22 +6983,22 @@
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D260" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E260" s="2">
+        <v>710000</v>
+      </c>
+      <c r="F260" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E260" s="6">
-        <v>220000</v>
-      </c>
-      <c r="F260" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="G260" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
@@ -6947,22 +7006,22 @@
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D261" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E261" s="6">
-        <v>710000</v>
+        <v>35</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E261" s="2">
+        <v>3408000</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
@@ -6970,22 +7029,399 @@
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E262" s="9">
+        <v>457218</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E263" s="10">
+        <v>565500</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E264" s="10">
+        <v>13961540</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E265" s="9">
+        <v>5738054</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E266" s="9">
+        <v>307409</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D267" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E267" s="9">
+        <v>2731488</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D268" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E268" s="9">
+        <v>19241672</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D269" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E269" s="9">
+        <v>18109573</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E270" s="9">
+        <v>7642330</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E271" s="9">
+        <v>126149</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E272" s="9">
+        <v>4879202</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D273" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E273" s="9">
+        <v>480490</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E274" s="9">
+        <v>270913</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E275" s="9">
+        <v>1362037</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E276" s="9">
+        <v>526155</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E277" s="9">
+        <v>2192715</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E278" s="9">
+        <v>6847946</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E279" s="9">
+        <v>811696</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E280" s="9">
+        <v>1417129</v>
+      </c>
+      <c r="F280" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C281" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D262" s="7" t="s">
+      <c r="D281" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E262" s="7">
-        <v>3408000</v>
-      </c>
-      <c r="F262" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>156</v>
+      <c r="E281" s="10">
+        <v>87669216</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
